--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129295065</v>
+        <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>106356</v>
+        <v>92388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590075</v>
+        <v>590096</v>
       </c>
       <c r="R4" t="n">
         <v>7043898</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,16 +980,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295065</t>
+          <t>https://artportalen.se/Sighting/137049977</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129295079</v>
+        <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>106356</v>
+        <v>92388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590069</v>
+        <v>590096</v>
       </c>
       <c r="R5" t="n">
-        <v>7043881</v>
+        <v>7043909</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,13 +1082,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295079</t>
+          <t>https://artportalen.se/Sighting/137050003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129295117</v>
+        <v>129295065</v>
       </c>
       <c r="B6" t="n">
         <v>106356</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590070</v>
+        <v>590075</v>
       </c>
       <c r="R6" t="n">
-        <v>7043906</v>
+        <v>7043898</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,38 +1184,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295117</t>
+          <t>https://artportalen.se/Sighting/129295065</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297218</v>
+        <v>129295079</v>
       </c>
       <c r="B7" t="n">
-        <v>91923</v>
+        <v>106356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590131</v>
+        <v>590069</v>
       </c>
       <c r="R7" t="n">
-        <v>7043983</v>
+        <v>7043881</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1286,38 +1286,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297218</t>
+          <t>https://artportalen.se/Sighting/129295079</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129296060</v>
+        <v>129295117</v>
       </c>
       <c r="B8" t="n">
-        <v>92333</v>
+        <v>106356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589919</v>
+        <v>590070</v>
       </c>
       <c r="R8" t="n">
-        <v>7043767</v>
+        <v>7043906</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1365,11 +1365,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1393,38 +1388,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296060</t>
+          <t>https://artportalen.se/Sighting/129295117</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129296017</v>
+        <v>129297218</v>
       </c>
       <c r="B9" t="n">
-        <v>80336</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589909</v>
+        <v>590131</v>
       </c>
       <c r="R9" t="n">
-        <v>7043766</v>
+        <v>7043983</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1495,38 +1490,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296017</t>
+          <t>https://artportalen.se/Sighting/129297218</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295993</v>
+        <v>129296060</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>92333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589921</v>
+        <v>589919</v>
       </c>
       <c r="R10" t="n">
-        <v>7043756</v>
+        <v>7043767</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,38 +1597,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295993</t>
+          <t>https://artportalen.se/Sighting/129296060</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297025</v>
+        <v>129296017</v>
       </c>
       <c r="B11" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590090</v>
+        <v>589909</v>
       </c>
       <c r="R11" t="n">
-        <v>7044059</v>
+        <v>7043766</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,13 +1699,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297025</t>
+          <t>https://artportalen.se/Sighting/129296017</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297136</v>
+        <v>129295993</v>
       </c>
       <c r="B12" t="n">
         <v>80432</v>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590098</v>
+        <v>589921</v>
       </c>
       <c r="R12" t="n">
-        <v>7044034</v>
+        <v>7043756</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1801,16 +1801,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297136</t>
+          <t>https://artportalen.se/Sighting/129295993</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129295440</v>
+        <v>129297025</v>
       </c>
       <c r="B13" t="n">
-        <v>10970</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,16 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590053</v>
+        <v>590090</v>
       </c>
       <c r="R13" t="n">
-        <v>7043912</v>
+        <v>7044059</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1898,16 +1903,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295440</t>
+          <t>https://artportalen.se/Sighting/129297025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296107</v>
+        <v>129297136</v>
       </c>
       <c r="B14" t="n">
-        <v>10970</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,16 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589881</v>
+        <v>590098</v>
       </c>
       <c r="R14" t="n">
-        <v>7043804</v>
+        <v>7044034</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,38 +2005,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296107</t>
+          <t>https://artportalen.se/Sighting/129297136</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295822</v>
+        <v>129295440</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>10970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589958</v>
+        <v>590053</v>
       </c>
       <c r="R15" t="n">
-        <v>7043777</v>
+        <v>7043912</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2074,11 +2079,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2102,38 +2102,33 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295822</t>
+          <t>https://artportalen.se/Sighting/129295440</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129295846</v>
+        <v>129296107</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>10970</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589946</v>
+        <v>589881</v>
       </c>
       <c r="R16" t="n">
-        <v>7043792</v>
+        <v>7043804</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2181,11 +2176,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2209,13 +2199,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295846</t>
+          <t>https://artportalen.se/Sighting/129296107</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129295920</v>
+        <v>129295822</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2250,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589923</v>
+        <v>589958</v>
       </c>
       <c r="R17" t="n">
-        <v>7043796</v>
+        <v>7043777</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2288,6 +2278,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2311,13 +2306,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295920</t>
+          <t>https://artportalen.se/Sighting/129295822</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129296228</v>
+        <v>129295846</v>
       </c>
       <c r="B18" t="n">
         <v>99118</v>
@@ -2352,13 +2347,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589928</v>
+        <v>589946</v>
       </c>
       <c r="R18" t="n">
-        <v>7043805</v>
+        <v>7043792</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,6 +2383,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,13 +2413,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296228</t>
+          <t>https://artportalen.se/Sighting/129295846</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129296341</v>
+        <v>129295920</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589967</v>
+        <v>589923</v>
       </c>
       <c r="R19" t="n">
-        <v>7043822</v>
+        <v>7043796</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2515,13 +2515,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296341</t>
+          <t>https://artportalen.se/Sighting/129295920</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129296395</v>
+        <v>129296228</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589988</v>
+        <v>589928</v>
       </c>
       <c r="R20" t="n">
-        <v>7043823</v>
+        <v>7043805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,38 +2617,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296395</t>
+          <t>https://artportalen.se/Sighting/129296228</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129295634</v>
+        <v>129296341</v>
       </c>
       <c r="B21" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590023</v>
+        <v>589967</v>
       </c>
       <c r="R21" t="n">
-        <v>7043880</v>
+        <v>7043822</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,38 +2719,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295634</t>
+          <t>https://artportalen.se/Sighting/129296341</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129296593</v>
+        <v>129296395</v>
       </c>
       <c r="B22" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590038</v>
+        <v>589988</v>
       </c>
       <c r="R22" t="n">
-        <v>7043930</v>
+        <v>7043823</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,16 +2821,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296593</t>
+          <t>https://artportalen.se/Sighting/129296395</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129295641</v>
+        <v>129295634</v>
       </c>
       <c r="B23" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2838,16 +2838,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590028</v>
+        <v>590023</v>
       </c>
       <c r="R23" t="n">
-        <v>7043891</v>
+        <v>7043880</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2922,6 +2922,210 @@
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295634</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129296593</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>590038</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7043930</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296593</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129295641</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>590028</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7043891</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129295641</t>
         </is>
@@ -2951,6 +3155,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129295065</v>
+        <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>106356</v>
+        <v>92388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590075</v>
+        <v>590092</v>
       </c>
       <c r="R6" t="n">
-        <v>7043898</v>
+        <v>7043911</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295065</t>
+          <t>https://artportalen.se/Sighting/137075817</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129295079</v>
+        <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>106356</v>
+        <v>92388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590069</v>
+        <v>590099</v>
       </c>
       <c r="R7" t="n">
-        <v>7043881</v>
+        <v>7043895</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,13 +1286,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295079</t>
+          <t>https://artportalen.se/Sighting/137075818</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129295117</v>
+        <v>129295065</v>
       </c>
       <c r="B8" t="n">
         <v>106356</v>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590070</v>
+        <v>590075</v>
       </c>
       <c r="R8" t="n">
-        <v>7043906</v>
+        <v>7043898</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1388,38 +1388,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295117</t>
+          <t>https://artportalen.se/Sighting/129295065</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297218</v>
+        <v>129295079</v>
       </c>
       <c r="B9" t="n">
-        <v>91923</v>
+        <v>106356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590131</v>
+        <v>590069</v>
       </c>
       <c r="R9" t="n">
-        <v>7043983</v>
+        <v>7043881</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,38 +1490,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297218</t>
+          <t>https://artportalen.se/Sighting/129295079</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129296060</v>
+        <v>129295117</v>
       </c>
       <c r="B10" t="n">
-        <v>92333</v>
+        <v>106356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589919</v>
+        <v>590070</v>
       </c>
       <c r="R10" t="n">
-        <v>7043767</v>
+        <v>7043906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1569,11 +1569,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1597,54 +1592,54 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296060</t>
+          <t>https://artportalen.se/Sighting/129295117</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129296017</v>
+        <v>137075825</v>
       </c>
       <c r="B11" t="n">
-        <v>80336</v>
+        <v>106615</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589909</v>
+        <v>590094</v>
       </c>
       <c r="R11" t="n">
-        <v>7043766</v>
+        <v>7043900</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,16 +1694,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296017</t>
+          <t>https://artportalen.se/Sighting/137075825</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129295993</v>
+        <v>137075826</v>
       </c>
       <c r="B12" t="n">
-        <v>80432</v>
+        <v>106615</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,37 +1711,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589921</v>
+        <v>590099</v>
       </c>
       <c r="R12" t="n">
-        <v>7043756</v>
+        <v>7043892</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1801,38 +1796,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295993</t>
+          <t>https://artportalen.se/Sighting/137075826</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297025</v>
+        <v>129297218</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590090</v>
+        <v>590131</v>
       </c>
       <c r="R13" t="n">
-        <v>7044059</v>
+        <v>7043983</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1903,38 +1898,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297025</t>
+          <t>https://artportalen.se/Sighting/129297218</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297136</v>
+        <v>129296060</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>92333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590098</v>
+        <v>589919</v>
       </c>
       <c r="R14" t="n">
-        <v>7044034</v>
+        <v>7043767</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1980,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,33 +2005,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297136</t>
+          <t>https://artportalen.se/Sighting/129296060</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295440</v>
+        <v>129296017</v>
       </c>
       <c r="B15" t="n">
-        <v>10970</v>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101449</v>
+        <v>6456</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590053</v>
+        <v>589909</v>
       </c>
       <c r="R15" t="n">
-        <v>7043912</v>
+        <v>7043766</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2102,16 +2107,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295440</t>
+          <t>https://artportalen.se/Sighting/129296017</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296107</v>
+        <v>129295993</v>
       </c>
       <c r="B16" t="n">
-        <v>10970</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,16 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101449</v>
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589881</v>
+        <v>589921</v>
       </c>
       <c r="R16" t="n">
-        <v>7043804</v>
+        <v>7043756</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2199,38 +2209,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296107</t>
+          <t>https://artportalen.se/Sighting/129295993</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129295822</v>
+        <v>129297025</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589958</v>
+        <v>590090</v>
       </c>
       <c r="R17" t="n">
-        <v>7043777</v>
+        <v>7044059</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2278,11 +2288,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2306,38 +2311,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295822</t>
+          <t>https://artportalen.se/Sighting/129297025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129295846</v>
+        <v>129297136</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589946</v>
+        <v>590098</v>
       </c>
       <c r="R18" t="n">
-        <v>7043792</v>
+        <v>7044034</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2383,11 +2388,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,38 +2413,33 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295846</t>
+          <t>https://artportalen.se/Sighting/129297136</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129295920</v>
+        <v>129295440</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>10970</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589923</v>
+        <v>590053</v>
       </c>
       <c r="R19" t="n">
-        <v>7043796</v>
+        <v>7043912</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2515,38 +2510,33 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295920</t>
+          <t>https://artportalen.se/Sighting/129295440</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129296228</v>
+        <v>129296107</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>10970</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>101449</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Olisthaerus substriatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Paykull, 1790)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2546,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589928</v>
+        <v>589881</v>
       </c>
       <c r="R20" t="n">
-        <v>7043805</v>
+        <v>7043804</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2617,54 +2607,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296228</t>
+          <t>https://artportalen.se/Sighting/129296107</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129296341</v>
+        <v>137074964</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>108386</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589967</v>
+        <v>590114</v>
       </c>
       <c r="R21" t="n">
-        <v>7043822</v>
+        <v>7043900</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2688,12 +2678,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,54 +2709,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296341</t>
+          <t>https://artportalen.se/Sighting/137074964</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129296395</v>
+        <v>137075851</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>111340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589988</v>
+        <v>590077</v>
       </c>
       <c r="R22" t="n">
-        <v>7043823</v>
+        <v>7043897</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2790,12 +2780,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2821,38 +2811,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296395</t>
+          <t>https://artportalen.se/Sighting/137075851</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129295634</v>
+        <v>129295822</v>
       </c>
       <c r="B23" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,13 +2852,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590023</v>
+        <v>589958</v>
       </c>
       <c r="R23" t="n">
-        <v>7043880</v>
+        <v>7043777</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2898,6 +2888,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2923,38 +2918,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295634</t>
+          <t>https://artportalen.se/Sighting/129295822</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129296593</v>
+        <v>129295846</v>
       </c>
       <c r="B24" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,13 +2959,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590038</v>
+        <v>589946</v>
       </c>
       <c r="R24" t="n">
-        <v>7043930</v>
+        <v>7043792</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3000,6 +2995,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,38 +3025,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296593</t>
+          <t>https://artportalen.se/Sighting/129295846</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129295641</v>
+        <v>129295920</v>
       </c>
       <c r="B25" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590028</v>
+        <v>589923</v>
       </c>
       <c r="R25" t="n">
-        <v>7043891</v>
+        <v>7043796</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3127,7 +3127,721 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/129295920</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129296228</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>589928</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7043805</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296228</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129296341</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>589967</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7043822</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296341</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129296395</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>589988</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7043823</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296395</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129295634</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>590023</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7043880</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295634</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129296593</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>590038</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7043930</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296593</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129295641</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>590028</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7043891</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129295641</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137075778</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101473</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lövbrännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>590108</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7043937</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137075778</t>
         </is>
       </c>
     </row>
@@ -3157,6 +3871,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137075825</v>
       </c>
       <c r="B11" t="n">
-        <v>106615</v>
+        <v>106616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137075826</v>
       </c>
       <c r="B12" t="n">
-        <v>106615</v>
+        <v>106616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137074964</v>
       </c>
       <c r="B21" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137075851</v>
       </c>
       <c r="B22" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>137075778</v>
       </c>
       <c r="B32" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137075825</v>
       </c>
       <c r="B11" t="n">
-        <v>106616</v>
+        <v>106622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137075826</v>
       </c>
       <c r="B12" t="n">
-        <v>106616</v>
+        <v>106622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137074964</v>
       </c>
       <c r="B21" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137075851</v>
       </c>
       <c r="B22" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>137075778</v>
       </c>
       <c r="B32" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129295065</v>
+        <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>106356</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590075</v>
+        <v>589913</v>
       </c>
       <c r="R8" t="n">
-        <v>7043898</v>
+        <v>7043766</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,16 +1388,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295065</t>
+          <t>https://artportalen.se/Sighting/137154059</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129295079</v>
+        <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>106356</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,37 +1405,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590069</v>
+        <v>589931</v>
       </c>
       <c r="R9" t="n">
-        <v>7043881</v>
+        <v>7043764</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,16 +1490,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295079</t>
+          <t>https://artportalen.se/Sighting/137154080</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129295117</v>
+        <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>106356</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590070</v>
+        <v>590082</v>
       </c>
       <c r="R10" t="n">
-        <v>7043906</v>
+        <v>7044096</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,16 +1592,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295117</t>
+          <t>https://artportalen.se/Sighting/137160707</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137075825</v>
+        <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>106622</v>
+        <v>92399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,37 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövbrännan, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590094</v>
+        <v>590134</v>
       </c>
       <c r="R11" t="n">
-        <v>7043900</v>
+        <v>7044115</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,16 +1694,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137075825</t>
+          <t>https://artportalen.se/Sighting/137160871</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137075826</v>
+        <v>129295065</v>
       </c>
       <c r="B12" t="n">
-        <v>106622</v>
+        <v>106356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,17 +1731,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lövbrännan, Ång</t>
+          <t>Stordalen, Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590099</v>
+        <v>590075</v>
       </c>
       <c r="R12" t="n">
-        <v>7043892</v>
+        <v>7043898</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,38 +1796,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137075826</t>
+          <t>https://artportalen.se/Sighting/129295065</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297218</v>
+        <v>129295079</v>
       </c>
       <c r="B13" t="n">
-        <v>91923</v>
+        <v>106356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590131</v>
+        <v>590069</v>
       </c>
       <c r="R13" t="n">
-        <v>7043983</v>
+        <v>7043881</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,38 +1898,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297218</t>
+          <t>https://artportalen.se/Sighting/129295079</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296060</v>
+        <v>129295117</v>
       </c>
       <c r="B14" t="n">
-        <v>92333</v>
+        <v>106356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589919</v>
+        <v>590070</v>
       </c>
       <c r="R14" t="n">
-        <v>7043767</v>
+        <v>7043906</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1977,11 +1977,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2005,54 +2000,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296060</t>
+          <t>https://artportalen.se/Sighting/129295117</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129296017</v>
+        <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>80336</v>
+        <v>106626</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589909</v>
+        <v>590094</v>
       </c>
       <c r="R15" t="n">
-        <v>7043766</v>
+        <v>7043900</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2076,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2107,16 +2102,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296017</t>
+          <t>https://artportalen.se/Sighting/137075825</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129295993</v>
+        <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>106626</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,37 +2119,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Lövbrännan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589921</v>
+        <v>590099</v>
       </c>
       <c r="R16" t="n">
-        <v>7043756</v>
+        <v>7043892</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2178,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2209,16 +2204,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295993</t>
+          <t>https://artportalen.se/Sighting/137075826</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129297025</v>
+        <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>106626</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,37 +2221,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590090</v>
+        <v>590085</v>
       </c>
       <c r="R17" t="n">
-        <v>7044059</v>
+        <v>7044070</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2280,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2311,54 +2306,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297025</t>
+          <t>https://artportalen.se/Sighting/137160420</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129297136</v>
+        <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>80432</v>
+        <v>92844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590098</v>
+        <v>590082</v>
       </c>
       <c r="R18" t="n">
-        <v>7044034</v>
+        <v>7044084</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2382,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,16 +2408,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297136</t>
+          <t>https://artportalen.se/Sighting/137160629</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129295440</v>
+        <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>10970</v>
+        <v>92128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,32 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101449</v>
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590053</v>
+        <v>590136</v>
       </c>
       <c r="R19" t="n">
-        <v>7043912</v>
+        <v>7044114</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2510,33 +2510,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295440</t>
+          <t>https://artportalen.se/Sighting/137160849</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129296107</v>
+        <v>129297218</v>
       </c>
       <c r="B20" t="n">
-        <v>10970</v>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101449</v>
+        <v>1204</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Olisthaerus substriatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Paykull, 1790)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2546,13 +2551,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589881</v>
+        <v>590131</v>
       </c>
       <c r="R20" t="n">
-        <v>7043804</v>
+        <v>7043983</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2607,16 +2612,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296107</t>
+          <t>https://artportalen.se/Sighting/129297218</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137074964</v>
+        <v>129296060</v>
       </c>
       <c r="B21" t="n">
-        <v>108393</v>
+        <v>92333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,37 +2629,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220083</v>
+        <v>4217</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lövbrännan, Ång</t>
+          <t>Stordalen, Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590114</v>
+        <v>589919</v>
       </c>
       <c r="R21" t="n">
-        <v>7043900</v>
+        <v>7043767</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2678,12 +2683,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,16 +2719,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074964</t>
+          <t>https://artportalen.se/Sighting/129296060</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137075851</v>
+        <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>111347</v>
+        <v>79509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,37 +2736,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220240</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lövbrännan, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
         <v>590077</v>
       </c>
       <c r="R22" t="n">
-        <v>7043897</v>
+        <v>7044174</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2780,12 +2790,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,38 +2821,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137075851</t>
+          <t>https://artportalen.se/Sighting/137151668</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129295822</v>
+        <v>129296017</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2852,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589958</v>
+        <v>589909</v>
       </c>
       <c r="R23" t="n">
-        <v>7043777</v>
+        <v>7043766</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2888,11 +2898,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,38 +2923,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295822</t>
+          <t>https://artportalen.se/Sighting/129296017</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129295846</v>
+        <v>129295993</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589946</v>
+        <v>589921</v>
       </c>
       <c r="R24" t="n">
-        <v>7043792</v>
+        <v>7043756</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2995,11 +3000,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,38 +3025,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295846</t>
+          <t>https://artportalen.se/Sighting/129295993</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129295920</v>
+        <v>129297025</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589923</v>
+        <v>590090</v>
       </c>
       <c r="R25" t="n">
-        <v>7043796</v>
+        <v>7044059</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3127,38 +3127,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295920</t>
+          <t>https://artportalen.se/Sighting/129297025</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129296228</v>
+        <v>129297136</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,13 +3168,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589928</v>
+        <v>590098</v>
       </c>
       <c r="R26" t="n">
-        <v>7043805</v>
+        <v>7044034</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3229,51 +3229,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296228</t>
+          <t>https://artportalen.se/Sighting/129297136</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129296341</v>
+        <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>80600</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589967</v>
+        <v>590103</v>
       </c>
       <c r="R27" t="n">
-        <v>7043822</v>
+        <v>7044207</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3300,12 +3303,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3314,6 +3317,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3331,51 +3335,51 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296341</t>
+          <t>https://artportalen.se/Sighting/137151599</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129296395</v>
+        <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>80600</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589988</v>
+        <v>590065</v>
       </c>
       <c r="R28" t="n">
-        <v>7043823</v>
+        <v>7044139</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3402,12 +3406,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3433,54 +3437,54 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296395</t>
+          <t>https://artportalen.se/Sighting/137152440</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129295634</v>
+        <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>97989</v>
+        <v>80600</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590023</v>
+        <v>590068</v>
       </c>
       <c r="R29" t="n">
-        <v>7043880</v>
+        <v>7044133</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3504,12 +3508,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3535,51 +3539,51 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295634</t>
+          <t>https://artportalen.se/Sighting/137152450</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129296593</v>
+        <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>97989</v>
+        <v>80600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590038</v>
+        <v>590079</v>
       </c>
       <c r="R30" t="n">
-        <v>7043930</v>
+        <v>7044123</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,12 +3610,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3637,54 +3641,54 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296593</t>
+          <t>https://artportalen.se/Sighting/137153255</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129295641</v>
+        <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>97983</v>
+        <v>80600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590028</v>
+        <v>589933</v>
       </c>
       <c r="R31" t="n">
-        <v>7043891</v>
+        <v>7043751</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3708,12 +3712,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3739,54 +3743,54 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129295641</t>
+          <t>https://artportalen.se/Sighting/137154402</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137075778</v>
+        <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>101480</v>
+        <v>80600</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lövbrännan, Ång</t>
+          <t>Stordalen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590108</v>
+        <v>589934</v>
       </c>
       <c r="R32" t="n">
-        <v>7043937</v>
+        <v>7043737</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3810,12 +3814,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3840,6 +3844,1851 @@
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137154454</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137153264</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80612</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>590080</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7044121</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153264</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129295440</v>
+      </c>
+      <c r="B34" t="n">
+        <v>10970</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101449</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Olisthaerus substriatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>590053</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7043912</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295440</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129296107</v>
+      </c>
+      <c r="B35" t="n">
+        <v>10970</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101449</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Olisthaerus substriatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>589881</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7043804</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296107</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137153917</v>
+      </c>
+      <c r="B36" t="n">
+        <v>10983</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101449</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Olisthaerus substriatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Paykull, 1790)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>589925</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7043796</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Under bark på grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153917</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137074964</v>
+      </c>
+      <c r="B37" t="n">
+        <v>108397</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lövbrännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>590114</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7043900</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074964</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137075851</v>
+      </c>
+      <c r="B38" t="n">
+        <v>111351</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lövbrännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>590077</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7043897</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137075851</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137153942</v>
+      </c>
+      <c r="B39" t="n">
+        <v>111351</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>589919</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7043796</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153942</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129295822</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>589958</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7043777</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295822</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129295846</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>589946</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7043792</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295846</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129295920</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>589923</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7043796</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295920</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129296228</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>589928</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7043805</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296228</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129296341</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>589967</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7043822</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296341</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129296395</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>589988</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7043823</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296395</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137154000</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>589911</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7043789</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137154000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129295634</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>590023</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7043880</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295634</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129296593</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>590038</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7043930</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296593</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129295641</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stordalen, Stordalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>590028</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7043891</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295641</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137075778</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101484</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lövbrännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>590108</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7043937</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137075778</t>
         </is>
@@ -3878,6 +5727,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106626</v>
+        <v>106628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106626</v>
+        <v>106628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106626</v>
+        <v>106628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106628</v>
+        <v>106630</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106628</v>
+        <v>106630</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106628</v>
+        <v>106630</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92844</v>
+        <v>92846</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106630</v>
+        <v>106643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106630</v>
+        <v>106643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106630</v>
+        <v>106643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92846</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106643</v>
+        <v>106645</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106643</v>
+        <v>106645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106643</v>
+        <v>106645</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>92861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>137153917</v>
       </c>
       <c r="B36" t="n">
-        <v>10983</v>
+        <v>10985</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -4175,11 +4175,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stordalen, Ång</t>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106645</v>
+        <v>106649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106645</v>
+        <v>106649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106645</v>
+        <v>106649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92861</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106649</v>
+        <v>106669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106649</v>
+        <v>106669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106649</v>
+        <v>106669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92864</v>
+        <v>92874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>137153917</v>
       </c>
       <c r="B36" t="n">
-        <v>10985</v>
+        <v>10991</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106669</v>
+        <v>106670</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106669</v>
+        <v>106670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106669</v>
+        <v>106670</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92874</v>
+        <v>92875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106670</v>
+        <v>106675</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106670</v>
+        <v>106675</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106670</v>
+        <v>106675</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92875</v>
+        <v>92878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106675</v>
+        <v>106678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106675</v>
+        <v>106678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106675</v>
+        <v>106678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92878</v>
+        <v>92880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106678</v>
+        <v>106684</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106678</v>
+        <v>106684</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106678</v>
+        <v>106684</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92880</v>
+        <v>92885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106684</v>
+        <v>106685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106684</v>
+        <v>106685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106684</v>
+        <v>106685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106685</v>
+        <v>106697</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106685</v>
+        <v>106697</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106685</v>
+        <v>106697</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92885</v>
+        <v>92897</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106697</v>
+        <v>106698</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106697</v>
+        <v>106698</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106697</v>
+        <v>106698</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92897</v>
+        <v>92898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106698</v>
+        <v>106701</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106698</v>
+        <v>106701</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106698</v>
+        <v>106701</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92898</v>
+        <v>92901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 12865-2024 artfynd.xlsx
+++ b/artfynd/A 12865-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137049977</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137050003</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137075817</v>
       </c>
       <c r="B6" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137075818</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137154059</v>
       </c>
       <c r="B8" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137154080</v>
       </c>
       <c r="B9" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137160707</v>
       </c>
       <c r="B10" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137160871</v>
       </c>
       <c r="B11" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137075825</v>
       </c>
       <c r="B15" t="n">
-        <v>106701</v>
+        <v>106707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137075826</v>
       </c>
       <c r="B16" t="n">
-        <v>106701</v>
+        <v>106707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137160420</v>
       </c>
       <c r="B17" t="n">
-        <v>106701</v>
+        <v>106707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137160629</v>
       </c>
       <c r="B18" t="n">
-        <v>92901</v>
+        <v>92905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137160849</v>
       </c>
       <c r="B19" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137151668</v>
       </c>
       <c r="B22" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>137151599</v>
       </c>
       <c r="B27" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137152440</v>
       </c>
       <c r="B28" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137152450</v>
       </c>
       <c r="B29" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>137153255</v>
       </c>
       <c r="B30" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>137154402</v>
       </c>
       <c r="B31" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137154454</v>
       </c>
       <c r="B32" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137153264</v>
       </c>
       <c r="B33" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>137074964</v>
       </c>
       <c r="B37" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137075851</v>
       </c>
       <c r="B38" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137153942</v>
       </c>
       <c r="B39" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>137154000</v>
       </c>
       <c r="B46" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137075778</v>
       </c>
       <c r="B50" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
